--- a/catalogs/Saturn-карточки-товаров-техданные.xlsx
+++ b/catalogs/Saturn-карточки-товаров-техданные.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Карточки товаров" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники и статус" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Что проверено и что осталось" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Карточки товаров'!$A$1:$M$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Карточки товаров'!$A$1:$M$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,14 +492,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="62" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
@@ -1418,10 +1418,14 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>от 48 ₽</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
+          <t>от 48 ₽ (МКР) · 54 ₽ (25 кг)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>МКР / 25 кг</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Бесхлорное калийное удобрение растительного происхождения с серой и магнием.</t>
@@ -1477,10 +1481,14 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>от 103 ₽</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
+          <t>от 103 ₽ (МКР 1000 кг) · 108 ₽ (мешки 35 кг)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>МКР 1000 кг / мешки 35 кг</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Концентрированное бесхлорное калийное удобрение с серой.</t>
@@ -3178,377 +3186,349 @@
     <row r="44" ht="76" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Микроэл</t>
+          <t>Relict Макро N Mg+</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Волски Биохим</t>
+          <t>Реликт</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Листовые подкормки</t>
+          <t>Удобрения</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>от 651 ₽</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>см. прайс</t>
-        </is>
-      </c>
+          <t>Цена по запросу</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Комплексное микроудобрение для листовых подкормок и поддержки фотосинтеза.</t>
+          <t>Азотно-серно-магниевое удобрение для листовых подкормок.</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Mn 3,4 · Mo 2,2 · MgO 15 · Zn 14 · Cu 6 · Fe 3,0 · Co 0,8 · B 1,6 · SO3 68 · N 4 · K2O 0,3 г/л; + Cr, Ni, Li, Se. 15 элементов, микро — хелат ЭДТА</t>
+          <t>Азот общий 250–280 г/л · сера (SO3) 40–50 г/л · магний (MgO) 7–10 г/л; плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>0,2–0,5 л/га, 2 обработки (при однократной — до 0,4 л/га). Рабочий раствор 30–300 л/га</t>
+          <t>Листовая подкормка</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Кукуруза 0,2 (5–9 лист, трубкование), подсолнечник 0,2, сах. свёкла 0,4, зернобобовые 0,2, озимые и яровые зерновые 0,2 (кущение, колошение), картофель 0,4, плодово-ягодные 0,5–1,0</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>канистра 10 л</t>
-        </is>
-      </c>
+          <t>Все декоративные и сельскохозяйственные культуры</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Плотность 1,3 г/см³</t>
+          <t>Плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Буклет ООО «Волски Биохим»</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr"/>
+          <t>Каталог ГК «Генезис» (2026)</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>нормы</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="76" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Моно-Бор</t>
+          <t>Relict Макро PK</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Волски Биохим</t>
+          <t>Реликт</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Листовые подкормки</t>
+          <t>Удобрения</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>от 760 ₽</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>см. прайс</t>
-        </is>
-      </c>
+          <t>Цена по запросу</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Борное микроудобрение для формирования цветков и плодов.</t>
+          <t>Фосфорно-калийное удобрение для налива и качества урожая.</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Бор 131 г/л (13,1%) · N 60 г/л (6%) · органический проникатель</t>
+          <t>Азот общий 65–90 г/л · фосфор (P2O5) 410–450 г/л · калий (K2O) 140–150 г/л; плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>0,5 л/га, 1–2 обработки (до 1 л/га при низком содержании бора). Рабочий раствор 100–300 л/га</t>
+          <t>Листовая подкормка</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Подсолнечник (формирование корзинки), сах. свёкла (перед смыканием рядков), картофель (смыкание рядков), горох/соя/рапс/горчица (бутонизация, перед цветением)</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>канистра 10 л</t>
-        </is>
-      </c>
+          <t>Все культуры; особенно масличные — подсолнечник, рапс, соя</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Плотность 1,3 г/см³</t>
+          <t>Плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>Буклет ООО «Волски Биохим»</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="inlineStr"/>
+          <t>Каталог ГК «Генезис» (2026)</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>нормы</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="76" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Моно-Цинк</t>
+          <t>OYYO Альфа Аминостарт</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Волски Биохим</t>
+          <t>OYYO</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Листовые подкормки</t>
+          <t>Удобрения</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>от 728 ₽</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>см. прайс</t>
-        </is>
-      </c>
+          <t>Цена по запросу</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Цинковое микроудобрение для фотосинтеза и устойчивого роста.</t>
+          <t>Органоминеральное удобрение с аминокислотами для стартового развития.</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Цинк 75 г/л (7,5%) · N 41 г/л (4,1%) · влагоудерживающий компонент</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>0,5 л/га, 1 обработка (до 1 л/га при низком содержании цинка). Рабочий раствор 100–300 л/га</t>
-        </is>
-      </c>
+          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 0,7% (мочевинный 0,1, аммонийный 0,1, нитратный 0,5) · P 0,5% · K 1,5% · Mg 0,08% · Ca 0,1% · Mn 0,0007% · Cu 0,0001% · Zn 0,0003% · Fe 0,07% · комплекс аминокислот и пептидов; рН 9,5–10,0</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Кукуруза (5–9 лист); другие культуры — рост листьев и стеблей</t>
+          <t>Все сельхозкультуры</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>канистра 10 л</t>
+          <t>1 л, 5 л</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Плотность 1,2 г/см³</t>
+          <t>Жидкое органоминеральное, рН 9,5–10,0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Буклет ООО «Волски Биохим»</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr"/>
+          <t>Каталог ГК «Генезис» (2026)</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>нормы</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="76" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Моно-Железо</t>
+          <t>OYYO Альфа Аминобиостим</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Волски Биохим</t>
+          <t>OYYO</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Листовые подкормки</t>
+          <t>Удобрения</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>от 430 ₽</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>см. прайс</t>
-        </is>
-      </c>
+          <t>Цена по запросу</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Хелатное железосодержащее микроудобрение для профилактики хлороза.</t>
+          <t>Органоминеральное удобрение для активного роста и восстановления.</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Железо 100 г/л (10%) · N 41 г/л (4,1%) · органический мембранный проникатель</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>Овощные и плодово-ягодные 0,5–1,0 л/га (1–3 обработки), зерновые 0,5 л/га (1 обработка). Рабочий раствор 100–300 л/га</t>
-        </is>
-      </c>
+          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 12% (мочевинный 8, аммонийный 2, нитратный 2) · P 4% · K 4% · Mg 0,08% · Ca 0,1% · Mn 0,01% · Cu 0,01% · Zn 0,01% · B 0,02% · Mo 0,01% · Fe 0,1% · аминокислоты и пептиды 2,0%; рН 6,3–6,8</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Овощные, зерновые, плодово-ягодные — при хлорозе и недостатке железа</t>
+          <t>Все сельхозкультуры</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>канистра 10 л</t>
+          <t>1 л, 5 л</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Плотность 1,3 г/см³</t>
+          <t>Жидкое органоминеральное, рН 6,3–6,8</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>Буклет ООО «Волски Биохим»</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr"/>
+          <t>Каталог ГК «Генезис» (2026)</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>нормы</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="76" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Моно-Сера</t>
+          <t>OYYO Альфа Аминофиниш</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Волски Биохим</t>
+          <t>OYYO</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Листовые подкормки</t>
+          <t>Удобрения</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>от 490 ₽</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>см. прайс</t>
-        </is>
-      </c>
+          <t>Цена по запросу</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Серное удобрение для эффективного азотного питания и качества урожая.</t>
+          <t>Высококалийное органоминеральное удобрение для налива урожая.</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Сера 72% · N 27 г/л (2,7%) · Mg 31 г/л (3,1%)</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>0,5–1,0 л/га (до 1 л/га при низком содержании серы). Рабочий раствор 100–300 л/га</t>
-        </is>
-      </c>
+          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 6% · P 4% · K 12% · S 4% · Mg 0,08% · Ca 0,1% · Mn 0,01% · Cu 0,001% · Zn 0,01% · B 0,02% · Mo 0,01% · Fe 0,1% · аминокислоты и пептиды 1,0%; рН 7,4–8,0</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr"/>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Рапс, сурепица, рыжик (3–7 лист — розетка); горох, соя, нут (3–4 лист — стеблевание); зерновые (колошение — флаговый лист)</t>
+          <t>Все сельхозкультуры — финальные стадии</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>канистра 10 л</t>
+          <t>1 л, 5 л</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Плотность 1,4 г/см³</t>
+          <t>Жидкое органоминеральное, рН 7,4–8,0</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Буклет ООО «Волски Биохим»</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr"/>
+          <t>Каталог ГК «Генезис» (2026)</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>нормы</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="76" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Моно-Медь</t>
+          <t>OYYO Альфа Старт</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Волски Биохим</t>
+          <t>OYYO</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Листовые подкормки</t>
+          <t>Удобрения</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>от 465 ₽</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>см. прайс</t>
-        </is>
-      </c>
+          <t>Цена по запросу</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Хелатное медное микроудобрение для обменных процессов и устойчивости.</t>
+          <t>Органоминеральное удобрение для начальных фаз роста и корней.</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Медь 82 г/л (8,2%) · N 41 г/л (4,1%) · органический мембранный проникатель</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>0,5–1,0 л/га. Рабочий раствор 100–300 л/га</t>
-        </is>
-      </c>
+          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 0,7% · P 0,5% · K 1,5% · Mg 0,08% · Ca 0,1% · Mn 0,0007% · Cu 0,0001% · Zn 0,0003% · Fe 0,07% · комплекс аминокислот и пептидов; рН 9,5–10,0</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Культуры при недостатке меди</t>
+          <t>Все сельхозкультуры</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>канистра 10 л</t>
+          <t>1 л, 5 л</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Плотность 1,2 г/см³</t>
+          <t>Жидкое органоминеральное, рН 9,5–10,0</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>Буклет ООО «Волски Биохим»</t>
+          <t>Каталог ГК «Генезис» (2026)</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -3560,12 +3540,12 @@
     <row r="50" ht="76" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Relict Р Старт</t>
+          <t>OYYO Биогель Амино</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Реликт</t>
+          <t>OYYO</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3575,32 +3555,36 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>от 735 ₽</t>
+          <t>Цена по запросу</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Гуминовый препарат с микроэлементами и Bacillus для обработки семян.</t>
+          <t>Органоминеральное удобрение с аминокислотами и гуминовыми веществами.</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Гуминовые и фульвокислоты 4–6% · хелатные микроэлементы (Mg, Fe, Mn, Cu, Zn) ≥0,4% · консорциум 4 штаммов рода Bacillus, титр ≥1×10⁷</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>Предпосевная обработка семян зерновых колосовых, обработка клубней и посадочного материала; возможны листовые обработки в вегетацию</t>
-        </is>
-      </c>
+          <t>N общий 5,4% (аммонийный 1,4, нитратный 4) · P 4,6% · K 15% · Ca 0,12% · S 5,1% · органическое вещество ≥1% (лизин, треонин, гуминовые и фульвовые кислоты) · индолилуксусная кислота 0,2%</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Пшеница, ячмень, рожь, картофель. Пролонгированная защита от корневых гнилей злаковых и ризоктониоза картофеля</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="3" t="inlineStr"/>
+          <t>Все сельхозкультуры</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>1 л, 5 л</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Гранулированное комплексное</t>
+        </is>
+      </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
           <t>Каталог ГК «Генезис» (2026)</t>
@@ -3615,12 +3599,12 @@
     <row r="51" ht="76" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Relict Макро N Mg+</t>
+          <t>OYYO Биогель Профи</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Реликт</t>
+          <t>OYYO</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3636,28 +3620,28 @@
       <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Азотно-серно-магниевое удобрение для листовых подкормок.</t>
+          <t>Комплексное органоминеральное удобрение с макро- и микроэлементами.</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>Азот общий 250–280 г/л · сера (SO3) 40–50 г/л · магний (MgO) 7–10 г/л; плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Листовая подкормка</t>
-        </is>
-      </c>
+          <t>N общий 12,4% (аммонийный 2,8, нитратный 9,6) · P 13,8% · K 5% · Mg 0,3% · S 1,7% · Fe 0,013% · Mn 0,01% · Cu 0,002% · Mo 0,001% · B 0,005% · органическое вещество ≥5% · ИУК 0,2%</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Все декоративные и сельскохозяйственные культуры</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr"/>
+          <t>Все сельхозкультуры</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>1 л, 5 л</t>
+        </is>
+      </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Плотность 1,2–1,3 г/см³, рН 5,5–7,5</t>
+          <t>Гранулированное комплексное</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3674,12 +3658,12 @@
     <row r="52" ht="76" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Relict Макро PK</t>
+          <t>OYYO Биогель Биостим</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Реликт</t>
+          <t>OYYO</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -3695,28 +3679,28 @@
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Фосфорно-калийное удобрение для налива и качества урожая.</t>
+          <t>Комплексное удобрение с повышенным калием и органическими компонентами.</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Азот общий 65–90 г/л · фосфор (P2O5) 410–450 г/л · калий (K2O) 140–150 г/л; плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>Листовая подкормка</t>
-        </is>
-      </c>
+          <t>N общий 7,2% (аммонийный 1,4, нитратный 5,8) · P 9,2% · K 25% · Ca 0,22% · Mg 1,5% · S 8,3% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Все культуры; особенно масличные — подсолнечник, рапс, соя</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr"/>
+          <t>Все сельхозкультуры</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>1 л, 5 л</t>
+        </is>
+      </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Плотность 1,35–1,45 г/см³, рН 6,5–7,5</t>
+          <t>Гранулированное комплексное</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -3733,7 +3717,7 @@
     <row r="53" ht="76" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>OYYO Альфа Аминостарт</t>
+          <t>OYYO Биогель Форте</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -3754,12 +3738,12 @@
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Органоминеральное удобрение с аминокислотами для стартового развития.</t>
+          <t>NPK-удобрение с органическими веществами и стимуляторами роста.</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 0,7% (мочевинный 0,1, аммонийный 0,1, нитратный 0,5) · P 0,5% · K 1,5% · Mg 0,08% · Ca 0,1% · Mn 0,0007% · Cu 0,0001% · Zn 0,0003% · Fe 0,07% · комплекс аминокислот и пептидов; рН 9,5–10,0</t>
+          <t>N общий 10% (аммонийный 5, нитратный 5) · P 10% · K 10% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr"/>
@@ -3775,7 +3759,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Жидкое органоминеральное, рН 9,5–10,0</t>
+          <t>Гранулированное комплексное</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3792,7 +3776,7 @@
     <row r="54" ht="76" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>OYYO Альфа Аминобиостим</t>
+          <t>OYYO Биогель Актив</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3813,18 +3797,18 @@
       <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Органоминеральное удобрение для активного роста и восстановления.</t>
+          <t>Фосфорное органоминеральное удобрение для корней и стартовых процессов.</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 12% (мочевинный 8, аммонийный 2, нитратный 2) · P 4% · K 4% · Mg 0,08% · Ca 0,1% · Mn 0,01% · Cu 0,01% · Zn 0,01% · B 0,02% · Mo 0,01% · Fe 0,1% · аминокислоты и пептиды 2,0%; рН 6,3–6,8</t>
+          <t>N общий 14,4% · P 40% · K 3,3% · S 0,45% · Fe 0,013% · Mn 0,01% · Cu 0,002% · Mo 0,001% · B 0,005% · органическое вещество ≥5% · ИУК 0,2%</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Все сельхозкультуры</t>
+          <t>Все сельхозкультуры — стартовые стадии</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -3834,7 +3818,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Жидкое органоминеральное, рН 6,3–6,8</t>
+          <t>Гранулированное комплексное</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -3851,7 +3835,7 @@
     <row r="55" ht="76" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>OYYO Альфа Аминофиниш</t>
+          <t>OYYO Биогель Универсал</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -3872,18 +3856,18 @@
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Высококалийное органоминеральное удобрение для налива урожая.</t>
+          <t>Универсальное комплексное удобрение для различных культур.</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 6% · P 4% · K 12% · S 4% · Mg 0,08% · Ca 0,1% · Mn 0,01% · Cu 0,001% · Zn 0,01% · B 0,02% · Mo 0,01% · Fe 0,1% · аминокислоты и пептиды 1,0%; рН 7,4–8,0</t>
+          <t>N общий 5% (аммонийный 2,5, нитратный 2,5) · P 5% · K 5% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Все сельхозкультуры — финальные стадии</t>
+          <t>Все сельхозкультуры</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
@@ -3893,7 +3877,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Жидкое органоминеральное, рН 7,4–8,0</t>
+          <t>Гранулированное комплексное</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -3910,7 +3894,7 @@
     <row r="56" ht="76" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>OYYO Альфа Старт</t>
+          <t>OYYO Биогель Старт</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3931,18 +3915,18 @@
       <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Органоминеральное удобрение для начальных фаз роста и корней.</t>
+          <t>Стартовое удобрение с фосфором и кальцием для корневой системы.</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Гуминовые и фульвовые кислоты ≥10% · N общий 0,7% · P 0,5% · K 1,5% · Mg 0,08% · Ca 0,1% · Mn 0,0007% · Cu 0,0001% · Zn 0,0003% · Fe 0,07% · комплекс аминокислот и пептидов; рН 9,5–10,0</t>
+          <t>N общий 3,6% · P 24% · Ca 4,8% · Mg 0,3% · S 4,8% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr"/>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Все сельхозкультуры</t>
+          <t>Все сельхозкультуры — стартовые стадии</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -3952,7 +3936,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Жидкое органоминеральное, рН 9,5–10,0</t>
+          <t>Гранулированное комплексное</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -3969,7 +3953,7 @@
     <row r="57" ht="76" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>OYYO Биогель Амино</t>
+          <t>OYYO Биогель Комплекс</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -3990,12 +3974,12 @@
       <c r="E57" s="7" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Органоминеральное удобрение с аминокислотами и гуминовыми веществами.</t>
+          <t>Комплексное органоминеральное удобрение с макро- и микроэлементами.</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>N общий 5,4% (аммонийный 1,4, нитратный 4) · P 4,6% · K 15% · Ca 0,12% · S 5,1% · органическое вещество ≥1% (лизин, треонин, гуминовые и фульвовые кислоты) · индолилуксусная кислота 0,2%</t>
+          <t>N общий 7% (аммонийный 2,8, нитратный 4,2) · P 10,3% · K 3,3% · Fe 0,013% · Mn 0,01% · Cu 0,002% · Mo 0,001% · B 0,005% · органическое вещество ≥1% · ИУК 0,2%</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr"/>
@@ -4025,421 +4009,8 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="76" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>OYYO Биогель Профи</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>OYYO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Удобрения</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>Комплексное органоминеральное удобрение с макро- и микроэлементами.</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>N общий 12,4% (аммонийный 2,8, нитратный 9,6) · P 13,8% · K 5% · Mg 0,3% · S 1,7% · Fe 0,013% · Mn 0,01% · Cu 0,002% · Mo 0,001% · B 0,005% · органическое вещество ≥5% · ИУК 0,2%</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>Все сельхозкультуры</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>1 л, 5 л</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>Гранулированное комплексное</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>Каталог ГК «Генезис» (2026)</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="76" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>OYYO Биогель Биостим</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>OYYO</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Удобрения</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Комплексное удобрение с повышенным калием и органическими компонентами.</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>N общий 7,2% (аммонийный 1,4, нитратный 5,8) · P 9,2% · K 25% · Ca 0,22% · Mg 1,5% · S 8,3% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Все сельхозкультуры</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>1 л, 5 л</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>Гранулированное комплексное</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>Каталог ГК «Генезис» (2026)</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="76" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>OYYO Биогель Форте</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>OYYO</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Удобрения</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>NPK-удобрение с органическими веществами и стимуляторами роста.</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>N общий 10% (аммонийный 5, нитратный 5) · P 10% · K 10% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>Все сельхозкультуры</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>1 л, 5 л</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>Гранулированное комплексное</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>Каталог ГК «Генезис» (2026)</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="76" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>OYYO Биогель Актив</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>OYYO</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Удобрения</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Фосфорное органоминеральное удобрение для корней и стартовых процессов.</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>N общий 14,4% · P 40% · K 3,3% · S 0,45% · Fe 0,013% · Mn 0,01% · Cu 0,002% · Mo 0,001% · B 0,005% · органическое вещество ≥5% · ИУК 0,2%</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Все сельхозкультуры — стартовые стадии</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>1 л, 5 л</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>Гранулированное комплексное</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>Каталог ГК «Генезис» (2026)</t>
-        </is>
-      </c>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="76" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>OYYO Биогель Универсал</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>OYYO</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Удобрения</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>Универсальное комплексное удобрение для различных культур.</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>N общий 5% (аммонийный 2,5, нитратный 2,5) · P 5% · K 5% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>Все сельхозкультуры</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>1 л, 5 л</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>Гранулированное комплексное</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>Каталог ГК «Генезис» (2026)</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="76" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>OYYO Биогель Старт</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>OYYO</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Удобрения</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Стартовое удобрение с фосфором и кальцием для корневой системы.</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>N общий 3,6% · P 24% · Ca 4,8% · Mg 0,3% · S 4,8% · органическое вещество ≥1% · индолилуксусная кислота 0,2%</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Все сельхозкультуры — стартовые стадии</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr">
-        <is>
-          <t>1 л, 5 л</t>
-        </is>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
-        <is>
-          <t>Гранулированное комплексное</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>Каталог ГК «Генезис» (2026)</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="76" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>OYYO Биогель Комплекс</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>OYYO</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Удобрения</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>Цена по запросу</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>Комплексное органоминеральное удобрение с макро- и микроэлементами.</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>N общий 7% (аммонийный 2,8, нитратный 4,2) · P 10,3% · K 3,3% · Fe 0,013% · Mn 0,01% · Cu 0,002% · Mo 0,001% · B 0,005% · органическое вещество ≥1% · ИУК 0,2%</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Все сельхозкультуры</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>1 л, 5 л</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>Гранулированное комплексное</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>Каталог ГК «Генезис» (2026)</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M64"/>
+  <autoFilter ref="A1:M57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4450,17 +4021,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Источники техданных</t>
+          <t>✅ ПРОВЕРЕНО</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr"/>
@@ -4468,120 +4039,180 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Фертика</t>
+          <t>Цены</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Каталог АО «Фертика» (PDF от заказчика) + fertika.com</t>
+          <t>Все 56 позиций сверены с листом «Прайс Сатурн» (прайс-лист сезон 2026, действителен с 12.01.2026). Расхождений нет.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Волски Биохим</t>
+          <t>Эко Калий / Сульфат калия</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Буклет ООО «Волски Биохим» (PDF от заказчика) + volskybiochem.com</t>
+          <t>В прайсе по ДВЕ цены — разная фасовка. Раньше в таблице стояла только одна. Теперь указаны обе.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Реликт / OYYO</t>
+          <t>Составы и нормы</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Каталог ГК «Генезис» (2026) — производитель продукции Relict Organics и OYYO</t>
+          <t>Сверены с каталогами производителей: Фертика, Волски Биохим, ГК «Генезис».</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr"/>
-      <c r="B5" s="10" t="inlineStr"/>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Дубли</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Удалено 7 дублей (Моно-* были записаны дважды — с приставкой «Волски» и без; «Микроэл» = «Микроэл Универсальный»; «Relict Р Старт» = «Реликт Р Старт»). Было 63 строки → 56 реальных позиций.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Что значит «Сверить»</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr"/>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Категории</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>«Relict Р Старт» стоял в «Удобрениях» — это протравитель семян, исправлено на «Обработка семян».</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>нормы</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Диапазоны норм восстановлены при извлечении текста из PDF (в исходнике потерялись дефисы: «2-4» → «24»). Перед публикацией сверить с сайтом производителя.</t>
-        </is>
-      </c>
+      <c r="A7" s="10" t="inlineStr"/>
+      <c r="B7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>нет данных</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>В каталогах производителей позиция не описана.</t>
-        </is>
-      </c>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>🔴 ОСТАЛОСЬ СДЕЛАТЬ</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr"/>
-      <c r="B9" s="10" t="inlineStr"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Раздел СЗР</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>В прайсе А4 есть большой раздел «Средства защиты растений» — гербициды, десиканты, протравители, инсектициды, фунгициды (~35 позиций). В таблицу он НЕ входит. Нужен исходный PDF для точного распознавания цен.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Открытые вопросы к заказчику</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr"/>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Адъюванты</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>«Вега 90», «Вега Голд», «Вега Клей», «Вега Турбо», «Вега Эмульс», «Волски Оптим», «Биостик Терра» — есть в прайсе, нет в таблице.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>OYYO</t>
+          <t>Фертика Газонное Осень</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Бренд ГК «Генезис». 12 позиций, цен в прайсе нет. Нужны цены и решение — показываем ли бренд на сайте.</t>
+          <t>Есть в прайсе (97 ₽), нет в таблице.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Генезис</t>
+          <t>Нормы расхода OYYO</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Решение заказчика: публично НЕ показываем. Продукция идёт под Relict Organics.</t>
+          <t>В каталоге Генезиса только составы. Запросить у заказчика.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Нормы расхода OYYO</t>
+          <t>Цены OYYO и Relict Макро</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>В каталоге Генезиса даны только составы, норм расхода нет. Запросить.</t>
+          <t>Нет ни в прайсе, ни в каталогах → «Цена по запросу». Запросить.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>📌 НАЙДЕНО ПОПУТНО</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>OYYO</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Бренд ГК «Генезис»: линейки «Альфа» (жидкие) и «Биогель» (гранулированные).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Отдел продаж</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>В прайсе 4 менеджера: Алексей +7 960 953-48-88, Андрей +7 963 502-38-55, Сергей +7 905 947-73-53, Виталий +7 960 948-83-40. У нас в документах было только двое.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Условия</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Прямая цитата из прайса: «В стоимость препаратов входит доставка, хранение, полное сопровождение по циклу от посевной до уборки урожая». Можно использовать на сайте.</t>
         </is>
       </c>
     </row>
